--- a/从零开始学Slots/从零开始学Slots-44-数值篇-Jackpot.xlsx
+++ b/从零开始学Slots/从零开始学Slots-44-数值篇-Jackpot.xlsx
@@ -8750,6 +8750,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N139" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -10146,5 +10149,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:M113" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-44-数值篇-Jackpot.xlsx
+++ b/从零开始学Slots/从零开始学Slots-44-数值篇-Jackpot.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="213">
   <si>
     <r>
       <rPr>
@@ -7779,7 +7779,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7934,6 +7934,22 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -8459,18 +8475,18 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="s">
-        <v>47</v>
+      <c r="A62" s="39">
+        <v>5</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="s">
-        <v>48</v>
+      <c r="A63" s="39">
+        <v>4</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="s">
-        <v>49</v>
+      <c r="A64" s="39">
+        <v>2</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8802,14 +8818,14 @@
       <c r="C4" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>90</v>
+      <c r="D4" s="40">
+        <v>3</v>
+      </c>
+      <c r="E4" s="40">
+        <v>4</v>
+      </c>
+      <c r="F4" s="40">
+        <v>5</v>
       </c>
       <c r="G4" s="13" t="s">
         <v>91</v>
@@ -9230,14 +9246,14 @@
       <c r="C30" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>143</v>
+      <c r="D30" s="40">
+        <v>5</v>
+      </c>
+      <c r="E30" s="40">
+        <v>4</v>
+      </c>
+      <c r="F30" s="40">
+        <v>3</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>144</v>
@@ -9471,8 +9487,8 @@
         <f aca="false">BINOMDIST($A46,15,$B$22,FALSE())</f>
         <v>0.00011045075461756</v>
       </c>
-      <c r="C46" s="29" t="s">
-        <v>163</v>
+      <c r="C46" s="41">
+        <v>15</v>
       </c>
       <c r="D46" s="29"/>
       <c r="E46" s="17"/>
@@ -9485,8 +9501,8 @@
         <f aca="false">BINOMDIST($A47,15,$B$22,FALSE())</f>
         <v>6.67664319795269E-006</v>
       </c>
-      <c r="C47" s="29" t="s">
-        <v>163</v>
+      <c r="C47" s="41">
+        <v>15</v>
       </c>
       <c r="D47" s="29"/>
       <c r="E47" s="17"/>
@@ -9499,8 +9515,8 @@
         <f aca="false">BINOMDIST($A48,15,$B$22,FALSE())</f>
         <v>3.11346055863079E-007</v>
       </c>
-      <c r="C48" s="29" t="s">
-        <v>163</v>
+      <c r="C48" s="41">
+        <v>15</v>
       </c>
       <c r="D48" s="29"/>
       <c r="E48" s="17"/>
@@ -9513,8 +9529,8 @@
         <f aca="false">BINOMDIST($A49,15,$B$22,FALSE())</f>
         <v>1.1292343995034E-008</v>
       </c>
-      <c r="C49" s="29" t="s">
-        <v>163</v>
+      <c r="C49" s="41">
+        <v>15</v>
       </c>
       <c r="D49" s="29"/>
       <c r="E49" s="17"/>
@@ -9527,8 +9543,8 @@
         <f aca="false">BINOMDIST($A50,15,$B$22,FALSE())</f>
         <v>3.18552018282478E-010</v>
       </c>
-      <c r="C50" s="29" t="s">
-        <v>163</v>
+      <c r="C50" s="41">
+        <v>15</v>
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="17"/>
@@ -9541,8 +9557,8 @@
         <f aca="false">BINOMDIST($A51,15,$B$22,FALSE())</f>
         <v>6.9322200869762E-012</v>
       </c>
-      <c r="C51" s="29" t="s">
-        <v>163</v>
+      <c r="C51" s="41">
+        <v>15</v>
       </c>
       <c r="D51" s="29"/>
       <c r="E51" s="17"/>
@@ -9555,8 +9571,8 @@
         <f aca="false">BINOMDIST($A52,15,$B$22,FALSE())</f>
         <v>1.14285305249254E-013</v>
       </c>
-      <c r="C52" s="29" t="s">
-        <v>163</v>
+      <c r="C52" s="41">
+        <v>15</v>
       </c>
       <c r="D52" s="29"/>
       <c r="E52" s="17"/>
@@ -9569,8 +9585,8 @@
         <f aca="false">BINOMDIST($A53,15,$B$22,FALSE())</f>
         <v>1.38168762822933E-015</v>
       </c>
-      <c r="C53" s="29" t="s">
-        <v>163</v>
+      <c r="C53" s="41">
+        <v>15</v>
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="17"/>
@@ -9583,8 +9599,8 @@
         <f aca="false">BINOMDIST($A54,15,$B$22,FALSE())</f>
         <v>1.15645437197353E-017</v>
       </c>
-      <c r="C54" s="29" t="s">
-        <v>163</v>
+      <c r="C54" s="41">
+        <v>15</v>
       </c>
       <c r="D54" s="29"/>
       <c r="E54" s="17"/>
@@ -9597,8 +9613,8 @@
         <f aca="false">BINOMDIST($A55,15,$B$22,FALSE())</f>
         <v>5.99199156462969E-020</v>
       </c>
-      <c r="C55" s="29" t="s">
-        <v>163</v>
+      <c r="C55" s="41">
+        <v>15</v>
       </c>
       <c r="D55" s="29"/>
       <c r="E55" s="17"/>
@@ -9611,8 +9627,8 @@
         <f aca="false">BINOMDIST($A56,15,$B$22,FALSE())</f>
         <v>1.44884079282929E-022</v>
       </c>
-      <c r="C56" s="29" t="s">
-        <v>163</v>
+      <c r="C56" s="41">
+        <v>15</v>
       </c>
       <c r="D56" s="29"/>
       <c r="E56" s="17"/>
@@ -9791,8 +9807,8 @@
       <c r="F71" s="31"/>
     </row>
     <row r="72" customFormat="false" ht="15.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="31" t="s">
-        <v>187</v>
+      <c r="A72" s="42">
+        <v>40</v>
       </c>
       <c r="B72" s="31"/>
       <c r="C72" s="31"/>
@@ -10076,8 +10092,8 @@
         <f aca="false">IF(ABS(B86-0.95)&lt;0.0001,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C92" s="29" t="s">
-        <v>210</v>
+      <c r="C92" s="41">
+        <v>0.8000</v>
       </c>
       <c r="D92" s="29"/>
       <c r="E92" s="17"/>
@@ -10091,8 +10107,8 @@
         <f aca="false">IF(ABS(C86-0.975)&lt;0.0001,"✓","✗")</f>
         <v>✓</v>
       </c>
-      <c r="C93" s="29" t="s">
-        <v>212</v>
+      <c r="C93" s="41">
+        <v>0.8432</v>
       </c>
       <c r="D93" s="29"/>
       <c r="E93" s="17"/>

--- a/从零开始学Slots/从零开始学Slots-44-数值篇-Jackpot.xlsx
+++ b/从零开始学Slots/从零开始学Slots-44-数值篇-Jackpot.xlsx
@@ -7589,13 +7589,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
     <numFmt numFmtId="168" formatCode="0.000000%"/>
     <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -7779,7 +7780,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7950,6 +7951,30 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9106,7 +9131,7 @@
       <c r="B19" s="19" t="n">
         <v>0.08</v>
       </c>
-      <c r="C19" s="20" t="n">
+      <c r="C19" s="44" t="n">
         <f aca="false">1-B19</f>
         <v>0.92</v>
       </c>
@@ -9122,7 +9147,7 @@
       <c r="B20" s="19" t="n">
         <v>0.03</v>
       </c>
-      <c r="C20" s="20" t="n">
+      <c r="C20" s="44" t="n">
         <f aca="false">1-B20</f>
         <v>0.97</v>
       </c>
@@ -9138,7 +9163,7 @@
       <c r="B21" s="19" t="n">
         <v>0.04</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C21" s="44" t="n">
         <f aca="false">1-B21</f>
         <v>0.96</v>
       </c>
@@ -9154,7 +9179,7 @@
       <c r="B22" s="19" t="n">
         <v>0.035</v>
       </c>
-      <c r="C22" s="20" t="n">
+      <c r="C22" s="44" t="n">
         <f aca="false">1-B22</f>
         <v>0.965</v>
       </c>
@@ -9194,11 +9219,11 @@
       <c r="A26" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="20" t="n">
+      <c r="B26" s="44" t="n">
         <f aca="false">B19+$B$21</f>
         <v>0.12</v>
       </c>
-      <c r="C26" s="20" t="n">
+      <c r="C26" s="44" t="n">
         <f aca="false">1-B26</f>
         <v>0.88</v>
       </c>
@@ -9211,11 +9236,11 @@
       <c r="A27" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="20" t="n">
+      <c r="B27" s="44" t="n">
         <f aca="false">B20+$B$21</f>
         <v>0.07</v>
       </c>
-      <c r="C27" s="20" t="n">
+      <c r="C27" s="44" t="n">
         <f aca="false">1-B27</f>
         <v>0.93</v>
       </c>
@@ -9263,27 +9288,27 @@
       <c r="A31" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="B31" s="22" t="n">
+      <c r="B31" s="45" t="n">
         <f aca="false">B26</f>
         <v>0.12</v>
       </c>
-      <c r="C31" s="22" t="n">
+      <c r="C31" s="45" t="n">
         <f aca="false">C26</f>
         <v>0.88</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="45" t="n">
         <f aca="false">B31^5*20</f>
         <v>0.000497664</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="45" t="n">
         <f aca="false">B31^4*C31*5</f>
         <v>0.000912384</v>
       </c>
-      <c r="F31" s="22" t="n">
+      <c r="F31" s="45" t="n">
         <f aca="false">B31^3*C31*2</f>
         <v>0.00304128</v>
       </c>
-      <c r="G31" s="22" t="n">
+      <c r="G31" s="45" t="n">
         <f aca="false">(D31+E31+F31)*5</f>
         <v>0.02225664</v>
       </c>
@@ -9292,27 +9317,27 @@
       <c r="A32" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B32" s="22" t="n">
+      <c r="B32" s="45" t="n">
         <f aca="false">B27</f>
         <v>0.07</v>
       </c>
-      <c r="C32" s="22" t="n">
+      <c r="C32" s="45" t="n">
         <f aca="false">C27</f>
         <v>0.93</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="45" t="n">
         <f aca="false">B32^5*100</f>
         <v>0.00016807</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="45" t="n">
         <f aca="false">B32^4*C32*25</f>
         <v>0.0005582325</v>
       </c>
-      <c r="F32" s="22" t="n">
+      <c r="F32" s="45" t="n">
         <f aca="false">B32^3*C32*5</f>
         <v>0.00159495</v>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="45" t="n">
         <f aca="false">(D32+E32+F32)*4</f>
         <v>0.00928501</v>
       </c>
@@ -9326,7 +9351,7 @@
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="46" t="n">
         <f aca="false">SUM(G31:G32)</f>
         <v>0.03154165</v>
       </c>
@@ -9441,7 +9466,7 @@
         <v>158</v>
       </c>
       <c r="B42" s="17"/>
-      <c r="C42" s="20" t="n">
+      <c r="C42" s="44" t="n">
         <f aca="false">SUM(C38:C41)</f>
         <v>1</v>
       </c>
@@ -9483,7 +9508,7 @@
       <c r="A46" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B46" s="28" t="n">
+      <c r="B46" s="47" t="n">
         <f aca="false">BINOMDIST($A46,15,$B$22,FALSE())</f>
         <v>0.00011045075461756</v>
       </c>
@@ -9497,7 +9522,7 @@
       <c r="A47" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B47" s="28" t="n">
+      <c r="B47" s="47" t="n">
         <f aca="false">BINOMDIST($A47,15,$B$22,FALSE())</f>
         <v>6.67664319795269E-006</v>
       </c>
@@ -9511,7 +9536,7 @@
       <c r="A48" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="B48" s="28" t="n">
+      <c r="B48" s="47" t="n">
         <f aca="false">BINOMDIST($A48,15,$B$22,FALSE())</f>
         <v>3.11346055863079E-007</v>
       </c>
@@ -9525,7 +9550,7 @@
       <c r="A49" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B49" s="28" t="n">
+      <c r="B49" s="47" t="n">
         <f aca="false">BINOMDIST($A49,15,$B$22,FALSE())</f>
         <v>1.1292343995034E-008</v>
       </c>
@@ -9539,7 +9564,7 @@
       <c r="A50" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="B50" s="28" t="n">
+      <c r="B50" s="47" t="n">
         <f aca="false">BINOMDIST($A50,15,$B$22,FALSE())</f>
         <v>3.18552018282478E-010</v>
       </c>
@@ -9553,7 +9578,7 @@
       <c r="A51" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B51" s="28" t="n">
+      <c r="B51" s="47" t="n">
         <f aca="false">BINOMDIST($A51,15,$B$22,FALSE())</f>
         <v>6.9322200869762E-012</v>
       </c>
@@ -9567,7 +9592,7 @@
       <c r="A52" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="B52" s="28" t="n">
+      <c r="B52" s="47" t="n">
         <f aca="false">BINOMDIST($A52,15,$B$22,FALSE())</f>
         <v>1.14285305249254E-013</v>
       </c>
@@ -9581,7 +9606,7 @@
       <c r="A53" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B53" s="28" t="n">
+      <c r="B53" s="47" t="n">
         <f aca="false">BINOMDIST($A53,15,$B$22,FALSE())</f>
         <v>1.38168762822933E-015</v>
       </c>
@@ -9595,7 +9620,7 @@
       <c r="A54" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="B54" s="28" t="n">
+      <c r="B54" s="47" t="n">
         <f aca="false">BINOMDIST($A54,15,$B$22,FALSE())</f>
         <v>1.15645437197353E-017</v>
       </c>
@@ -9609,7 +9634,7 @@
       <c r="A55" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B55" s="28" t="n">
+      <c r="B55" s="47" t="n">
         <f aca="false">BINOMDIST($A55,15,$B$22,FALSE())</f>
         <v>5.99199156462969E-020</v>
       </c>
@@ -9623,7 +9648,7 @@
       <c r="A56" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="B56" s="28" t="n">
+      <c r="B56" s="47" t="n">
         <f aca="false">BINOMDIST($A56,15,$B$22,FALSE())</f>
         <v>1.44884079282929E-022</v>
       </c>
@@ -9637,7 +9662,7 @@
       <c r="A57" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="30" t="n">
+      <c r="B57" s="48" t="n">
         <f aca="false">SUM(B46:B56)</f>
         <v>0.000117450361815288</v>
       </c>
@@ -9690,7 +9715,7 @@
       <c r="A62" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="B62" s="22" t="n">
+      <c r="B62" s="45" t="n">
         <f aca="false">G33</f>
         <v>0.03154165</v>
       </c>
@@ -9704,7 +9729,7 @@
       <c r="A63" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="B63" s="22" t="n">
+      <c r="B63" s="45" t="n">
         <f aca="false">B62*B61</f>
         <v>0.630833</v>
       </c>
@@ -9732,7 +9757,7 @@
       <c r="A65" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="B65" s="28" t="n">
+      <c r="B65" s="47" t="n">
         <f aca="false">B57</f>
         <v>0.000117450361815288</v>
       </c>
@@ -9746,7 +9771,7 @@
       <c r="A66" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="B66" s="22" t="n">
+      <c r="B66" s="45" t="n">
         <f aca="false">B65*B64</f>
         <v>0.0263088810466245</v>
       </c>
@@ -9761,7 +9786,7 @@
       <c r="A67" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B67" s="23" t="n">
+      <c r="B67" s="46" t="n">
         <f aca="false">B63+B66</f>
         <v>0.657141881046625</v>
       </c>
@@ -9854,7 +9879,7 @@
       <c r="B76" s="25" t="n">
         <v>2500</v>
       </c>
-      <c r="C76" s="20" t="n">
+      <c r="C76" s="44" t="n">
         <f aca="false">B76/10000</f>
         <v>0.25</v>
       </c>
@@ -9874,7 +9899,7 @@
       <c r="B77" s="25" t="n">
         <v>2500</v>
       </c>
-      <c r="C77" s="20" t="n">
+      <c r="C77" s="44" t="n">
         <f aca="false">B77/10000</f>
         <v>0.25</v>
       </c>
@@ -9894,7 +9919,7 @@
       <c r="B78" s="25" t="n">
         <v>2500</v>
       </c>
-      <c r="C78" s="20" t="n">
+      <c r="C78" s="44" t="n">
         <f aca="false">B78/10000</f>
         <v>0.25</v>
       </c>
@@ -9914,7 +9939,7 @@
       <c r="B79" s="25" t="n">
         <v>2500</v>
       </c>
-      <c r="C79" s="20" t="n">
+      <c r="C79" s="44" t="n">
         <f aca="false">B79/10000</f>
         <v>0.25</v>
       </c>
@@ -9935,7 +9960,7 @@
         <f aca="false">SUM(B76:B79)</f>
         <v>10000</v>
       </c>
-      <c r="C80" s="20" t="n">
+      <c r="C80" s="44" t="n">
         <f aca="false">B80/10000</f>
         <v>1</v>
       </c>
